--- a/output/yearly_population_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_30_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4773</v>
+        <v>4730</v>
       </c>
       <c r="C2" t="n">
-        <v>10039</v>
+        <v>4641</v>
       </c>
       <c r="D2" t="n">
-        <v>22025</v>
+        <v>25202</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3258</v>
+        <v>3351</v>
       </c>
       <c r="C3" t="n">
-        <v>4997</v>
+        <v>5475</v>
       </c>
       <c r="D3" t="n">
-        <v>12160</v>
+        <v>17305</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2420</v>
+        <v>2286</v>
       </c>
       <c r="C4" t="n">
-        <v>5295</v>
+        <v>5945</v>
       </c>
       <c r="D4" t="n">
-        <v>5856</v>
+        <v>8862</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1597</v>
+        <v>1467</v>
       </c>
       <c r="C5" t="n">
-        <v>3978</v>
+        <v>4759</v>
       </c>
       <c r="D5" t="n">
-        <v>2303</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>916</v>
+        <v>843</v>
       </c>
       <c r="C6" t="n">
-        <v>3311</v>
+        <v>2844</v>
       </c>
       <c r="D6" t="n">
-        <v>1053</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
-        <v>2463</v>
+        <v>1614</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>1364</v>
+        <v>796</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>548</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -954,7 +954,7 @@
         <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1052,7 +1052,7 @@
         <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5803</v>
+        <v>5143</v>
       </c>
       <c r="C2" t="n">
-        <v>13995</v>
+        <v>14658</v>
       </c>
       <c r="D2" t="n">
-        <v>21117</v>
+        <v>35915</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3203</v>
+        <v>3273</v>
       </c>
       <c r="C3" t="n">
-        <v>6381</v>
+        <v>4484</v>
       </c>
       <c r="D3" t="n">
-        <v>12684</v>
+        <v>17216</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>2339</v>
       </c>
       <c r="C4" t="n">
-        <v>4993</v>
+        <v>5595</v>
       </c>
       <c r="D4" t="n">
-        <v>6706</v>
+        <v>9970</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1724</v>
+        <v>1605</v>
       </c>
       <c r="C5" t="n">
-        <v>4502</v>
+        <v>5160</v>
       </c>
       <c r="D5" t="n">
-        <v>2756</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1108</v>
+        <v>1011</v>
       </c>
       <c r="C6" t="n">
-        <v>3541</v>
+        <v>3680</v>
       </c>
       <c r="D6" t="n">
-        <v>1230</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>570</v>
+        <v>533</v>
       </c>
       <c r="C7" t="n">
-        <v>2835</v>
+        <v>2139</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C8" t="n">
-        <v>1813</v>
+        <v>1148</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>878</v>
+        <v>530</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>267</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>106</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1363,7 +1363,7 @@
         <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6440</v>
+        <v>6467</v>
       </c>
       <c r="C2" t="n">
-        <v>15847</v>
+        <v>8218</v>
       </c>
       <c r="D2" t="n">
-        <v>29355</v>
+        <v>33462</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3456</v>
+        <v>3292</v>
       </c>
       <c r="C3" t="n">
-        <v>8407</v>
+        <v>7644</v>
       </c>
       <c r="D3" t="n">
-        <v>12884</v>
+        <v>18358</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="C4" t="n">
-        <v>5440</v>
+        <v>4944</v>
       </c>
       <c r="D4" t="n">
-        <v>7298</v>
+        <v>10614</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1763</v>
+        <v>1681</v>
       </c>
       <c r="C5" t="n">
-        <v>4615</v>
+        <v>5186</v>
       </c>
       <c r="D5" t="n">
-        <v>3241</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1233</v>
+        <v>1135</v>
       </c>
       <c r="C6" t="n">
-        <v>3862</v>
+        <v>4257</v>
       </c>
       <c r="D6" t="n">
-        <v>1407</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>700</v>
+        <v>647</v>
       </c>
       <c r="C7" t="n">
-        <v>3089</v>
+        <v>2736</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>853</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="C8" t="n">
-        <v>2212</v>
+        <v>1536</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>1217</v>
+        <v>754</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>544</v>
+        <v>359</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1674,7 +1674,7 @@
         <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5924</v>
+        <v>5909</v>
       </c>
       <c r="C2" t="n">
-        <v>10902</v>
+        <v>5588</v>
       </c>
       <c r="D2" t="n">
-        <v>24102</v>
+        <v>27650</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4165</v>
+        <v>4064</v>
       </c>
       <c r="C3" t="n">
-        <v>12091</v>
+        <v>10365</v>
       </c>
       <c r="D3" t="n">
-        <v>13992</v>
+        <v>20003</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1629</v>
+        <v>1553</v>
       </c>
       <c r="C4" t="n">
-        <v>7407</v>
+        <v>7683</v>
       </c>
       <c r="D4" t="n">
-        <v>7004</v>
+        <v>10256</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1139</v>
+        <v>1048</v>
       </c>
       <c r="C5" t="n">
-        <v>3784</v>
+        <v>4171</v>
       </c>
       <c r="D5" t="n">
-        <v>2250</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>646</v>
+        <v>597</v>
       </c>
       <c r="C6" t="n">
-        <v>3027</v>
+        <v>2681</v>
       </c>
       <c r="D6" t="n">
-        <v>741</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>2167</v>
+        <v>1505</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>1192</v>
+        <v>738</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>533</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1971,7 +1971,7 @@
         <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3592</v>
+        <v>3538</v>
       </c>
       <c r="C2" t="n">
-        <v>5310</v>
+        <v>2808</v>
       </c>
       <c r="D2" t="n">
-        <v>16784</v>
+        <v>19186</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4237</v>
+        <v>4176</v>
       </c>
       <c r="C3" t="n">
-        <v>10483</v>
+        <v>7454</v>
       </c>
       <c r="D3" t="n">
-        <v>14695</v>
+        <v>20082</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2247</v>
+        <v>2169</v>
       </c>
       <c r="C4" t="n">
-        <v>9695</v>
+        <v>8980</v>
       </c>
       <c r="D4" t="n">
-        <v>7864</v>
+        <v>11446</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1262</v>
+        <v>1173</v>
       </c>
       <c r="C5" t="n">
-        <v>5347</v>
+        <v>5734</v>
       </c>
       <c r="D5" t="n">
-        <v>2818</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>3436</v>
+        <v>3359</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>2584</v>
+        <v>1933</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>1514</v>
+        <v>979</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>585</v>
+        <v>394</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>97</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2268,7 +2268,7 @@
         <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3216</v>
+        <v>3450</v>
       </c>
       <c r="C2" t="n">
-        <v>12357</v>
+        <v>9166</v>
       </c>
       <c r="D2" t="n">
-        <v>15703</v>
+        <v>22009</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3336</v>
+        <v>3287</v>
       </c>
       <c r="C3" t="n">
-        <v>7097</v>
+        <v>4674</v>
       </c>
       <c r="D3" t="n">
-        <v>13991</v>
+        <v>18610</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2667</v>
+        <v>2586</v>
       </c>
       <c r="C4" t="n">
-        <v>9972</v>
+        <v>8046</v>
       </c>
       <c r="D4" t="n">
-        <v>8739</v>
+        <v>12507</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1414</v>
       </c>
       <c r="C5" t="n">
-        <v>7239</v>
+        <v>7196</v>
       </c>
       <c r="D5" t="n">
-        <v>3507</v>
+        <v>5026</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>833</v>
       </c>
       <c r="C6" t="n">
-        <v>4280</v>
+        <v>4375</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
-        <v>2941</v>
+        <v>2566</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>1958</v>
+        <v>1371</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>942</v>
+        <v>615</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2579,7 +2579,7 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1934</v>
+        <v>2032</v>
       </c>
       <c r="C2" t="n">
-        <v>5876</v>
+        <v>4277</v>
       </c>
       <c r="D2" t="n">
-        <v>10949</v>
+        <v>15380</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3193</v>
+        <v>3236</v>
       </c>
       <c r="C3" t="n">
-        <v>8617</v>
+        <v>6041</v>
       </c>
       <c r="D3" t="n">
-        <v>13855</v>
+        <v>18546</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2929</v>
+        <v>2828</v>
       </c>
       <c r="C4" t="n">
-        <v>9811</v>
+        <v>7550</v>
       </c>
       <c r="D4" t="n">
-        <v>9380</v>
+        <v>13302</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1552</v>
+        <v>1476</v>
       </c>
       <c r="C5" t="n">
-        <v>8863</v>
+        <v>8519</v>
       </c>
       <c r="D5" t="n">
-        <v>3709</v>
+        <v>5296</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>734</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>5241</v>
+        <v>5205</v>
       </c>
       <c r="D6" t="n">
-        <v>1150</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>3255</v>
+        <v>2611</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1518</v>
+        <v>1019</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2792,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2876,7 +2876,7 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3012</v>
+        <v>2693</v>
       </c>
       <c r="C2" t="n">
-        <v>9798</v>
+        <v>5184</v>
       </c>
       <c r="D2" t="n">
-        <v>18465</v>
+        <v>14995</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2278</v>
+        <v>2348</v>
       </c>
       <c r="C3" t="n">
-        <v>6604</v>
+        <v>4668</v>
       </c>
       <c r="D3" t="n">
-        <v>12661</v>
+        <v>17047</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2683</v>
+        <v>2641</v>
       </c>
       <c r="C4" t="n">
-        <v>9056</v>
+        <v>6755</v>
       </c>
       <c r="D4" t="n">
-        <v>9782</v>
+        <v>13703</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1862</v>
+        <v>1784</v>
       </c>
       <c r="C5" t="n">
-        <v>9182</v>
+        <v>7995</v>
       </c>
       <c r="D5" t="n">
-        <v>4412</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>888</v>
       </c>
       <c r="C6" t="n">
-        <v>6740</v>
+        <v>6577</v>
       </c>
       <c r="D6" t="n">
-        <v>1478</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>4096</v>
+        <v>3677</v>
       </c>
       <c r="D7" t="n">
-        <v>634</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2159</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>730</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3173,7 +3173,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2015</v>
+        <v>1750</v>
       </c>
       <c r="C2" t="n">
-        <v>4815</v>
+        <v>2896</v>
       </c>
       <c r="D2" t="n">
-        <v>14582</v>
+        <v>11702</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2197</v>
+        <v>2154</v>
       </c>
       <c r="C3" t="n">
-        <v>7111</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>12642</v>
+        <v>16037</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2368</v>
+        <v>2355</v>
       </c>
       <c r="C4" t="n">
-        <v>8163</v>
+        <v>5967</v>
       </c>
       <c r="D4" t="n">
-        <v>9937</v>
+        <v>13835</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1994</v>
+        <v>1945</v>
       </c>
       <c r="C5" t="n">
-        <v>9211</v>
+        <v>7695</v>
       </c>
       <c r="D5" t="n">
-        <v>4929</v>
+        <v>6939</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>1037</v>
       </c>
       <c r="C6" t="n">
-        <v>7752</v>
+        <v>7277</v>
       </c>
       <c r="D6" t="n">
-        <v>1714</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C7" t="n">
-        <v>4997</v>
+        <v>4609</v>
       </c>
       <c r="D7" t="n">
-        <v>699</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2676</v>
+        <v>2071</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>811</v>
+        <v>592</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2881</v>
+        <v>2689</v>
       </c>
       <c r="C2" t="n">
-        <v>12134</v>
+        <v>11917</v>
       </c>
       <c r="D2" t="n">
-        <v>15254</v>
+        <v>16659</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1797</v>
+        <v>1696</v>
       </c>
       <c r="C3" t="n">
-        <v>5547</v>
+        <v>3397</v>
       </c>
       <c r="D3" t="n">
-        <v>12187</v>
+        <v>14490</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2027</v>
+        <v>1986</v>
       </c>
       <c r="C4" t="n">
-        <v>7558</v>
+        <v>5190</v>
       </c>
       <c r="D4" t="n">
-        <v>9903</v>
+        <v>13731</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>1902</v>
       </c>
       <c r="C5" t="n">
-        <v>8606</v>
+        <v>6838</v>
       </c>
       <c r="D5" t="n">
-        <v>5452</v>
+        <v>7654</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1296</v>
+        <v>1247</v>
       </c>
       <c r="C6" t="n">
-        <v>8234</v>
+        <v>7376</v>
       </c>
       <c r="D6" t="n">
-        <v>2093</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="C7" t="n">
-        <v>6042</v>
+        <v>5645</v>
       </c>
       <c r="D7" t="n">
-        <v>811</v>
+        <v>961</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>3448</v>
+        <v>2940</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1403</v>
+        <v>1075</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5106</v>
+        <v>4407</v>
       </c>
       <c r="C2" t="n">
-        <v>15919</v>
+        <v>5580</v>
       </c>
       <c r="D2" t="n">
-        <v>5467</v>
+        <v>8918</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2104</v>
+        <v>1943</v>
       </c>
       <c r="C2" t="n">
-        <v>7087</v>
+        <v>6864</v>
       </c>
       <c r="D2" t="n">
-        <v>11348</v>
+        <v>12394</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2412</v>
+        <v>2303</v>
       </c>
       <c r="C3" t="n">
-        <v>7539</v>
+        <v>5604</v>
       </c>
       <c r="D3" t="n">
-        <v>13314</v>
+        <v>15766</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2823</v>
+        <v>2771</v>
       </c>
       <c r="C4" t="n">
-        <v>10471</v>
+        <v>7474</v>
       </c>
       <c r="D4" t="n">
-        <v>10054</v>
+        <v>14095</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1215</v>
+        <v>1187</v>
       </c>
       <c r="C5" t="n">
-        <v>12069</v>
+        <v>10253</v>
       </c>
       <c r="D5" t="n">
-        <v>4971</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C6" t="n">
-        <v>7373</v>
+        <v>6905</v>
       </c>
       <c r="D6" t="n">
-        <v>1696</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>3379</v>
+        <v>2881</v>
       </c>
       <c r="D7" t="n">
-        <v>528</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>1053</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6070</v>
+        <v>5732</v>
       </c>
       <c r="C2" t="n">
-        <v>6696</v>
+        <v>7111</v>
       </c>
       <c r="D2" t="n">
-        <v>15487</v>
+        <v>28856</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2170</v>
+        <v>1874</v>
       </c>
       <c r="C3" t="n">
-        <v>8023</v>
+        <v>2856</v>
       </c>
       <c r="D3" t="n">
-        <v>1557</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4651</v>
+        <v>4088</v>
       </c>
       <c r="C2" t="n">
-        <v>5148</v>
+        <v>4789</v>
       </c>
       <c r="D2" t="n">
-        <v>14609</v>
+        <v>24955</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3382</v>
+        <v>3121</v>
       </c>
       <c r="C3" t="n">
-        <v>6271</v>
+        <v>4539</v>
       </c>
       <c r="D3" t="n">
-        <v>3782</v>
+        <v>6468</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>977</v>
+        <v>848</v>
       </c>
       <c r="C4" t="n">
-        <v>4744</v>
+        <v>1717</v>
       </c>
       <c r="D4" t="n">
-        <v>1495</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4583</v>
+        <v>4116</v>
       </c>
       <c r="C2" t="n">
-        <v>3453</v>
+        <v>5091</v>
       </c>
       <c r="D2" t="n">
-        <v>20284</v>
+        <v>35402</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3292</v>
+        <v>2958</v>
       </c>
       <c r="C3" t="n">
-        <v>4917</v>
+        <v>4046</v>
       </c>
       <c r="D3" t="n">
-        <v>5242</v>
+        <v>8960</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1853</v>
+        <v>1685</v>
       </c>
       <c r="C4" t="n">
-        <v>5450</v>
+        <v>3279</v>
       </c>
       <c r="D4" t="n">
-        <v>1888</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>453</v>
+        <v>401</v>
       </c>
       <c r="C5" t="n">
-        <v>2692</v>
+        <v>1034</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5167</v>
+        <v>4727</v>
       </c>
       <c r="C2" t="n">
-        <v>8239</v>
+        <v>9391</v>
       </c>
       <c r="D2" t="n">
-        <v>22448</v>
+        <v>28949</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3201</v>
+        <v>2883</v>
       </c>
       <c r="C3" t="n">
-        <v>3643</v>
+        <v>3989</v>
       </c>
       <c r="D3" t="n">
-        <v>7159</v>
+        <v>12348</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2158</v>
+        <v>1974</v>
       </c>
       <c r="C4" t="n">
-        <v>5002</v>
+        <v>3623</v>
       </c>
       <c r="D4" t="n">
-        <v>2442</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>949</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>4065</v>
+        <v>2166</v>
       </c>
       <c r="D5" t="n">
-        <v>1274</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>1492</v>
+        <v>670</v>
       </c>
       <c r="D6" t="n">
         <v>946</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5643</v>
+        <v>4729</v>
       </c>
       <c r="C2" t="n">
-        <v>6053</v>
+        <v>10608</v>
       </c>
       <c r="D2" t="n">
-        <v>21198</v>
+        <v>27817</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3000</v>
+        <v>2744</v>
       </c>
       <c r="C3" t="n">
-        <v>4874</v>
+        <v>5529</v>
       </c>
       <c r="D3" t="n">
-        <v>8447</v>
+        <v>13173</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1642</v>
+        <v>1497</v>
       </c>
       <c r="C4" t="n">
-        <v>3489</v>
+        <v>3132</v>
       </c>
       <c r="D4" t="n">
-        <v>2816</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>802</v>
+        <v>739</v>
       </c>
       <c r="C5" t="n">
-        <v>3279</v>
+        <v>2118</v>
       </c>
       <c r="D5" t="n">
-        <v>1154</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>1861</v>
+        <v>959</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>570</v>
+        <v>323</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4403</v>
+        <v>4989</v>
       </c>
       <c r="C2" t="n">
-        <v>9320</v>
+        <v>7134</v>
       </c>
       <c r="D2" t="n">
-        <v>24539</v>
+        <v>36678</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3574</v>
+        <v>3103</v>
       </c>
       <c r="C3" t="n">
-        <v>4781</v>
+        <v>7310</v>
       </c>
       <c r="D3" t="n">
-        <v>9967</v>
+        <v>14663</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2014</v>
+        <v>1864</v>
       </c>
       <c r="C4" t="n">
-        <v>4254</v>
+        <v>4516</v>
       </c>
       <c r="D4" t="n">
-        <v>3838</v>
+        <v>6022</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1091</v>
+        <v>998</v>
       </c>
       <c r="C5" t="n">
-        <v>3333</v>
+        <v>2667</v>
       </c>
       <c r="D5" t="n">
-        <v>1453</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="C6" t="n">
-        <v>2641</v>
+        <v>1594</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>1290</v>
+        <v>684</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>409</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4744</v>
+        <v>5009</v>
       </c>
       <c r="C2" t="n">
-        <v>5177</v>
+        <v>6293</v>
       </c>
       <c r="D2" t="n">
-        <v>21147</v>
+        <v>26538</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3309</v>
+        <v>3304</v>
       </c>
       <c r="C3" t="n">
-        <v>6252</v>
+        <v>6244</v>
       </c>
       <c r="D3" t="n">
-        <v>11580</v>
+        <v>17129</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2371</v>
+        <v>2137</v>
       </c>
       <c r="C4" t="n">
-        <v>4458</v>
+        <v>6004</v>
       </c>
       <c r="D4" t="n">
-        <v>4898</v>
+        <v>7498</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1360</v>
+        <v>1244</v>
       </c>
       <c r="C5" t="n">
-        <v>3726</v>
+        <v>3623</v>
       </c>
       <c r="D5" t="n">
-        <v>1829</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>713</v>
+        <v>661</v>
       </c>
       <c r="C6" t="n">
-        <v>2976</v>
+        <v>2142</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>1991</v>
+        <v>1149</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>845</v>
+        <v>484</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6650,7 +6650,7 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_30_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4730</v>
+        <v>6064</v>
       </c>
       <c r="C2" t="n">
-        <v>4641</v>
+        <v>7043</v>
       </c>
       <c r="D2" t="n">
-        <v>25202</v>
+        <v>25191</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3351</v>
+        <v>3678</v>
       </c>
       <c r="C3" t="n">
-        <v>5475</v>
+        <v>6306</v>
       </c>
       <c r="D3" t="n">
-        <v>17305</v>
+        <v>15036</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2286</v>
+        <v>2861</v>
       </c>
       <c r="C4" t="n">
-        <v>5945</v>
+        <v>5468</v>
       </c>
       <c r="D4" t="n">
-        <v>8862</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1467</v>
+        <v>1987</v>
       </c>
       <c r="C5" t="n">
-        <v>4759</v>
+        <v>4982</v>
       </c>
       <c r="D5" t="n">
-        <v>3387</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>843</v>
+        <v>1171</v>
       </c>
       <c r="C6" t="n">
-        <v>2844</v>
+        <v>3371</v>
       </c>
       <c r="D6" t="n">
-        <v>1297</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>553</v>
       </c>
       <c r="C7" t="n">
-        <v>1614</v>
+        <v>1824</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="C8" t="n">
-        <v>796</v>
+        <v>727</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -954,7 +954,7 @@
         <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5143</v>
+        <v>9312</v>
       </c>
       <c r="C2" t="n">
-        <v>14658</v>
+        <v>5580</v>
       </c>
       <c r="D2" t="n">
-        <v>35915</v>
+        <v>32184</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3273</v>
+        <v>3886</v>
       </c>
       <c r="C3" t="n">
-        <v>4484</v>
+        <v>5844</v>
       </c>
       <c r="D3" t="n">
-        <v>17216</v>
+        <v>15406</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2339</v>
+        <v>2747</v>
       </c>
       <c r="C4" t="n">
-        <v>5595</v>
+        <v>5756</v>
       </c>
       <c r="D4" t="n">
-        <v>9970</v>
+        <v>7639</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1605</v>
+        <v>2094</v>
       </c>
       <c r="C5" t="n">
-        <v>5160</v>
+        <v>5054</v>
       </c>
       <c r="D5" t="n">
-        <v>4092</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1011</v>
+        <v>1386</v>
       </c>
       <c r="C6" t="n">
-        <v>3680</v>
+        <v>4064</v>
       </c>
       <c r="D6" t="n">
-        <v>1600</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>533</v>
+        <v>738</v>
       </c>
       <c r="C7" t="n">
-        <v>2139</v>
+        <v>2487</v>
       </c>
       <c r="D7" t="n">
-        <v>752</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>307</v>
       </c>
       <c r="C8" t="n">
-        <v>1148</v>
+        <v>1199</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
-        <v>530</v>
+        <v>478</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>181</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6467</v>
+        <v>10135</v>
       </c>
       <c r="C2" t="n">
-        <v>8218</v>
+        <v>6830</v>
       </c>
       <c r="D2" t="n">
-        <v>33462</v>
+        <v>33036</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3292</v>
+        <v>4883</v>
       </c>
       <c r="C3" t="n">
-        <v>7644</v>
+        <v>5094</v>
       </c>
       <c r="D3" t="n">
-        <v>18358</v>
+        <v>16433</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2335</v>
+        <v>2756</v>
       </c>
       <c r="C4" t="n">
-        <v>4944</v>
+        <v>5619</v>
       </c>
       <c r="D4" t="n">
-        <v>10614</v>
+        <v>8451</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1681</v>
+        <v>2100</v>
       </c>
       <c r="C5" t="n">
-        <v>5186</v>
+        <v>5196</v>
       </c>
       <c r="D5" t="n">
-        <v>4814</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>1522</v>
       </c>
       <c r="C6" t="n">
-        <v>4257</v>
+        <v>4436</v>
       </c>
       <c r="D6" t="n">
-        <v>1898</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>647</v>
+        <v>892</v>
       </c>
       <c r="C7" t="n">
-        <v>2736</v>
+        <v>3095</v>
       </c>
       <c r="D7" t="n">
-        <v>853</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303</v>
+        <v>417</v>
       </c>
       <c r="C8" t="n">
-        <v>1536</v>
+        <v>1703</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C9" t="n">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="D9" t="n">
         <v>330</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1548,7 +1548,7 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5909</v>
+        <v>9199</v>
       </c>
       <c r="C2" t="n">
-        <v>5588</v>
+        <v>4644</v>
       </c>
       <c r="D2" t="n">
-        <v>27650</v>
+        <v>27217</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4064</v>
+        <v>5426</v>
       </c>
       <c r="C3" t="n">
-        <v>10365</v>
+        <v>8029</v>
       </c>
       <c r="D3" t="n">
-        <v>20003</v>
+        <v>17583</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1553</v>
+        <v>1940</v>
       </c>
       <c r="C4" t="n">
-        <v>7683</v>
+        <v>8062</v>
       </c>
       <c r="D4" t="n">
-        <v>10256</v>
+        <v>7862</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1048</v>
+        <v>1406</v>
       </c>
       <c r="C5" t="n">
-        <v>4171</v>
+        <v>4347</v>
       </c>
       <c r="D5" t="n">
-        <v>3154</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>597</v>
+        <v>824</v>
       </c>
       <c r="C6" t="n">
-        <v>2681</v>
+        <v>3033</v>
       </c>
       <c r="D6" t="n">
-        <v>835</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>1505</v>
+        <v>1668</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="D8" t="n">
         <v>323</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1845,7 +1845,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3538</v>
+        <v>5517</v>
       </c>
       <c r="C2" t="n">
-        <v>2808</v>
+        <v>2370</v>
       </c>
       <c r="D2" t="n">
-        <v>19186</v>
+        <v>18935</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4176</v>
+        <v>5994</v>
       </c>
       <c r="C3" t="n">
-        <v>7454</v>
+        <v>5902</v>
       </c>
       <c r="D3" t="n">
-        <v>20082</v>
+        <v>17880</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2169</v>
+        <v>2811</v>
       </c>
       <c r="C4" t="n">
-        <v>8980</v>
+        <v>8111</v>
       </c>
       <c r="D4" t="n">
-        <v>11446</v>
+        <v>9267</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1173</v>
+        <v>1543</v>
       </c>
       <c r="C5" t="n">
-        <v>5734</v>
+        <v>5998</v>
       </c>
       <c r="D5" t="n">
-        <v>4005</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>969</v>
       </c>
       <c r="C6" t="n">
-        <v>3359</v>
+        <v>3642</v>
       </c>
       <c r="D6" t="n">
-        <v>1071</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>1933</v>
+        <v>2189</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3450</v>
+        <v>4878</v>
       </c>
       <c r="C2" t="n">
-        <v>9166</v>
+        <v>3961</v>
       </c>
       <c r="D2" t="n">
-        <v>22009</v>
+        <v>17632</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3287</v>
+        <v>4859</v>
       </c>
       <c r="C3" t="n">
-        <v>4674</v>
+        <v>3762</v>
       </c>
       <c r="D3" t="n">
-        <v>18610</v>
+        <v>16973</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2586</v>
+        <v>3605</v>
       </c>
       <c r="C4" t="n">
-        <v>8046</v>
+        <v>6860</v>
       </c>
       <c r="D4" t="n">
-        <v>12507</v>
+        <v>10390</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1414</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>7196</v>
+        <v>6867</v>
       </c>
       <c r="D5" t="n">
-        <v>5026</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>833</v>
+        <v>1113</v>
       </c>
       <c r="C6" t="n">
-        <v>4375</v>
+        <v>4705</v>
       </c>
       <c r="D6" t="n">
-        <v>1479</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>532</v>
       </c>
       <c r="C7" t="n">
-        <v>2566</v>
+        <v>2836</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>1371</v>
+        <v>1481</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2032</v>
+        <v>2915</v>
       </c>
       <c r="C2" t="n">
-        <v>4277</v>
+        <v>1864</v>
       </c>
       <c r="D2" t="n">
-        <v>15380</v>
+        <v>12329</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3236</v>
+        <v>4691</v>
       </c>
       <c r="C3" t="n">
-        <v>6041</v>
+        <v>3714</v>
       </c>
       <c r="D3" t="n">
-        <v>18546</v>
+        <v>16661</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2828</v>
+        <v>3992</v>
       </c>
       <c r="C4" t="n">
-        <v>7550</v>
+        <v>6364</v>
       </c>
       <c r="D4" t="n">
-        <v>13302</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1476</v>
+        <v>1940</v>
       </c>
       <c r="C5" t="n">
-        <v>8519</v>
+        <v>7876</v>
       </c>
       <c r="D5" t="n">
-        <v>5296</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>944</v>
       </c>
       <c r="C6" t="n">
-        <v>5205</v>
+        <v>5665</v>
       </c>
       <c r="D6" t="n">
-        <v>1436</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>2611</v>
+        <v>2891</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1019</v>
+        <v>1040</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2693</v>
+        <v>3820</v>
       </c>
       <c r="C2" t="n">
-        <v>5184</v>
+        <v>7481</v>
       </c>
       <c r="D2" t="n">
-        <v>14995</v>
+        <v>12853</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2348</v>
+        <v>3394</v>
       </c>
       <c r="C3" t="n">
-        <v>4668</v>
+        <v>2543</v>
       </c>
       <c r="D3" t="n">
-        <v>17047</v>
+        <v>14952</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2641</v>
+        <v>3735</v>
       </c>
       <c r="C4" t="n">
-        <v>6755</v>
+        <v>5020</v>
       </c>
       <c r="D4" t="n">
-        <v>13703</v>
+        <v>11733</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1784</v>
+        <v>2443</v>
       </c>
       <c r="C5" t="n">
-        <v>7995</v>
+        <v>7105</v>
       </c>
       <c r="D5" t="n">
-        <v>6287</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>888</v>
+        <v>1210</v>
       </c>
       <c r="C6" t="n">
-        <v>6577</v>
+        <v>6602</v>
       </c>
       <c r="D6" t="n">
-        <v>1936</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>3677</v>
+        <v>4061</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1600</v>
+        <v>1731</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1750</v>
+        <v>2865</v>
       </c>
       <c r="C2" t="n">
-        <v>2896</v>
+        <v>3665</v>
       </c>
       <c r="D2" t="n">
-        <v>11702</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2154</v>
+        <v>3093</v>
       </c>
       <c r="C3" t="n">
-        <v>4423</v>
+        <v>4084</v>
       </c>
       <c r="D3" t="n">
-        <v>16037</v>
+        <v>13886</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2355</v>
+        <v>3317</v>
       </c>
       <c r="C4" t="n">
-        <v>5967</v>
+        <v>4037</v>
       </c>
       <c r="D4" t="n">
-        <v>13835</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1945</v>
+        <v>2695</v>
       </c>
       <c r="C5" t="n">
-        <v>7695</v>
+        <v>6469</v>
       </c>
       <c r="D5" t="n">
-        <v>6939</v>
+        <v>5766</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>1426</v>
       </c>
       <c r="C6" t="n">
-        <v>7277</v>
+        <v>7035</v>
       </c>
       <c r="D6" t="n">
-        <v>2345</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="C7" t="n">
-        <v>4609</v>
+        <v>4960</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>2071</v>
+        <v>2268</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3366,10 +3366,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>625</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2689</v>
+        <v>4644</v>
       </c>
       <c r="C2" t="n">
-        <v>11917</v>
+        <v>3856</v>
       </c>
       <c r="D2" t="n">
-        <v>16659</v>
+        <v>21665</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1696</v>
+        <v>2534</v>
       </c>
       <c r="C3" t="n">
-        <v>3397</v>
+        <v>3475</v>
       </c>
       <c r="D3" t="n">
-        <v>14490</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1986</v>
+        <v>2813</v>
       </c>
       <c r="C4" t="n">
-        <v>5190</v>
+        <v>3973</v>
       </c>
       <c r="D4" t="n">
-        <v>13731</v>
+        <v>11841</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1902</v>
+        <v>2679</v>
       </c>
       <c r="C5" t="n">
-        <v>6838</v>
+        <v>5330</v>
       </c>
       <c r="D5" t="n">
-        <v>7654</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1247</v>
+        <v>1707</v>
       </c>
       <c r="C6" t="n">
-        <v>7376</v>
+        <v>6751</v>
       </c>
       <c r="D6" t="n">
-        <v>2888</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>611</v>
       </c>
       <c r="C7" t="n">
-        <v>5645</v>
+        <v>5799</v>
       </c>
       <c r="D7" t="n">
-        <v>961</v>
+        <v>851</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>2940</v>
+        <v>3216</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1075</v>
+        <v>1178</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4407</v>
+        <v>6408</v>
       </c>
       <c r="C2" t="n">
-        <v>5580</v>
+        <v>4156</v>
       </c>
       <c r="D2" t="n">
-        <v>8918</v>
+        <v>4949</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1943</v>
+        <v>3323</v>
       </c>
       <c r="C2" t="n">
-        <v>6864</v>
+        <v>2190</v>
       </c>
       <c r="D2" t="n">
-        <v>12394</v>
+        <v>15945</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2303</v>
+        <v>3454</v>
       </c>
       <c r="C3" t="n">
-        <v>5604</v>
+        <v>3863</v>
       </c>
       <c r="D3" t="n">
-        <v>15766</v>
+        <v>14213</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2771</v>
+        <v>3911</v>
       </c>
       <c r="C4" t="n">
-        <v>7474</v>
+        <v>5818</v>
       </c>
       <c r="D4" t="n">
-        <v>14095</v>
+        <v>12111</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1187</v>
+        <v>1651</v>
       </c>
       <c r="C5" t="n">
-        <v>10253</v>
+        <v>8772</v>
       </c>
       <c r="D5" t="n">
-        <v>6926</v>
+        <v>5739</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>400</v>
+        <v>564</v>
       </c>
       <c r="C6" t="n">
-        <v>6905</v>
+        <v>7006</v>
       </c>
       <c r="D6" t="n">
-        <v>2234</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>2881</v>
+        <v>3151</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1053</v>
+        <v>1154</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5732</v>
+        <v>7294</v>
       </c>
       <c r="C2" t="n">
-        <v>7111</v>
+        <v>5492</v>
       </c>
       <c r="D2" t="n">
-        <v>28856</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1874</v>
+        <v>2722</v>
       </c>
       <c r="C3" t="n">
-        <v>2856</v>
+        <v>2127</v>
       </c>
       <c r="D3" t="n">
-        <v>2137</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4088</v>
+        <v>6289</v>
       </c>
       <c r="C2" t="n">
-        <v>4789</v>
+        <v>8628</v>
       </c>
       <c r="D2" t="n">
-        <v>24955</v>
+        <v>12816</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3121</v>
+        <v>4112</v>
       </c>
       <c r="C3" t="n">
-        <v>4539</v>
+        <v>3499</v>
       </c>
       <c r="D3" t="n">
-        <v>6468</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>848</v>
+        <v>1216</v>
       </c>
       <c r="C4" t="n">
-        <v>1717</v>
+        <v>1309</v>
       </c>
       <c r="D4" t="n">
-        <v>1612</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4116</v>
+        <v>5537</v>
       </c>
       <c r="C2" t="n">
-        <v>5091</v>
+        <v>10775</v>
       </c>
       <c r="D2" t="n">
-        <v>35402</v>
+        <v>17916</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2958</v>
+        <v>4302</v>
       </c>
       <c r="C3" t="n">
-        <v>4046</v>
+        <v>5449</v>
       </c>
       <c r="D3" t="n">
-        <v>8960</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1685</v>
+        <v>2255</v>
       </c>
       <c r="C4" t="n">
-        <v>3279</v>
+        <v>2509</v>
       </c>
       <c r="D4" t="n">
-        <v>2495</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>401</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>1034</v>
+        <v>821</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4727</v>
+        <v>6054</v>
       </c>
       <c r="C2" t="n">
-        <v>9391</v>
+        <v>5229</v>
       </c>
       <c r="D2" t="n">
-        <v>28949</v>
+        <v>24739</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2883</v>
+        <v>4024</v>
       </c>
       <c r="C3" t="n">
-        <v>3989</v>
+        <v>7162</v>
       </c>
       <c r="D3" t="n">
-        <v>12348</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1974</v>
+        <v>2760</v>
       </c>
       <c r="C4" t="n">
-        <v>3623</v>
+        <v>4065</v>
       </c>
       <c r="D4" t="n">
-        <v>3598</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>853</v>
+        <v>1173</v>
       </c>
       <c r="C5" t="n">
-        <v>2166</v>
+        <v>1695</v>
       </c>
       <c r="D5" t="n">
-        <v>1395</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>242</v>
+        <v>304</v>
       </c>
       <c r="C6" t="n">
-        <v>670</v>
+        <v>560</v>
       </c>
       <c r="D6" t="n">
         <v>946</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4729</v>
+        <v>6151</v>
       </c>
       <c r="C2" t="n">
-        <v>10608</v>
+        <v>10103</v>
       </c>
       <c r="D2" t="n">
-        <v>27817</v>
+        <v>35412</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2744</v>
+        <v>3663</v>
       </c>
       <c r="C3" t="n">
-        <v>5529</v>
+        <v>5099</v>
       </c>
       <c r="D3" t="n">
-        <v>13173</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1497</v>
+        <v>2120</v>
       </c>
       <c r="C4" t="n">
-        <v>3132</v>
+        <v>4698</v>
       </c>
       <c r="D4" t="n">
-        <v>4439</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>739</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="n">
-        <v>2118</v>
+        <v>2158</v>
       </c>
       <c r="D5" t="n">
-        <v>1393</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>257</v>
+        <v>352</v>
       </c>
       <c r="C6" t="n">
-        <v>959</v>
+        <v>759</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4989</v>
+        <v>5555</v>
       </c>
       <c r="C2" t="n">
-        <v>7134</v>
+        <v>5640</v>
       </c>
       <c r="D2" t="n">
-        <v>36678</v>
+        <v>29208</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3103</v>
+        <v>4074</v>
       </c>
       <c r="C3" t="n">
-        <v>7310</v>
+        <v>6934</v>
       </c>
       <c r="D3" t="n">
-        <v>14663</v>
+        <v>12219</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1864</v>
+        <v>2539</v>
       </c>
       <c r="C4" t="n">
-        <v>4516</v>
+        <v>4846</v>
       </c>
       <c r="D4" t="n">
-        <v>6022</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>998</v>
+        <v>1392</v>
       </c>
       <c r="C5" t="n">
-        <v>2667</v>
+        <v>3624</v>
       </c>
       <c r="D5" t="n">
-        <v>1964</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>458</v>
+        <v>640</v>
       </c>
       <c r="C6" t="n">
-        <v>1594</v>
+        <v>1555</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>684</v>
+        <v>557</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5009</v>
+        <v>5080</v>
       </c>
       <c r="C2" t="n">
-        <v>6293</v>
+        <v>9087</v>
       </c>
       <c r="D2" t="n">
-        <v>26538</v>
+        <v>27574</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3304</v>
+        <v>3947</v>
       </c>
       <c r="C3" t="n">
-        <v>6244</v>
+        <v>5391</v>
       </c>
       <c r="D3" t="n">
-        <v>17129</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2137</v>
+        <v>2825</v>
       </c>
       <c r="C4" t="n">
-        <v>6004</v>
+        <v>5927</v>
       </c>
       <c r="D4" t="n">
-        <v>7498</v>
+        <v>5083</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1244</v>
+        <v>1732</v>
       </c>
       <c r="C5" t="n">
-        <v>3623</v>
+        <v>4182</v>
       </c>
       <c r="D5" t="n">
-        <v>2625</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>916</v>
       </c>
       <c r="C6" t="n">
-        <v>2142</v>
+        <v>2649</v>
       </c>
       <c r="D6" t="n">
-        <v>1069</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>373</v>
       </c>
       <c r="C7" t="n">
-        <v>1149</v>
+        <v>1084</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>484</v>
+        <v>411</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_30_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6064</v>
+        <v>1130</v>
       </c>
       <c r="C2" t="n">
-        <v>7043</v>
+        <v>1875</v>
       </c>
       <c r="D2" t="n">
-        <v>25191</v>
+        <v>13661</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3678</v>
+        <v>2377</v>
       </c>
       <c r="C3" t="n">
-        <v>6306</v>
+        <v>4789</v>
       </c>
       <c r="D3" t="n">
-        <v>15036</v>
+        <v>13398</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>2013</v>
       </c>
       <c r="C4" t="n">
-        <v>5468</v>
+        <v>6578</v>
       </c>
       <c r="D4" t="n">
-        <v>6430</v>
+        <v>5114</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1987</v>
+        <v>1131</v>
       </c>
       <c r="C5" t="n">
-        <v>4982</v>
+        <v>4012</v>
       </c>
       <c r="D5" t="n">
-        <v>2221</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1171</v>
+        <v>454</v>
       </c>
       <c r="C6" t="n">
-        <v>3371</v>
+        <v>1818</v>
       </c>
       <c r="D6" t="n">
-        <v>1003</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>553</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>1824</v>
+        <v>749</v>
       </c>
       <c r="D7" t="n">
-        <v>633</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>727</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9312</v>
+        <v>2044</v>
       </c>
       <c r="C2" t="n">
-        <v>5580</v>
+        <v>4540</v>
       </c>
       <c r="D2" t="n">
-        <v>32184</v>
+        <v>17907</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3886</v>
+        <v>1507</v>
       </c>
       <c r="C3" t="n">
-        <v>5844</v>
+        <v>2815</v>
       </c>
       <c r="D3" t="n">
-        <v>15406</v>
+        <v>12604</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2747</v>
+        <v>1912</v>
       </c>
       <c r="C4" t="n">
-        <v>5756</v>
+        <v>5508</v>
       </c>
       <c r="D4" t="n">
-        <v>7639</v>
+        <v>6469</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2094</v>
+        <v>1371</v>
       </c>
       <c r="C5" t="n">
-        <v>5054</v>
+        <v>5283</v>
       </c>
       <c r="D5" t="n">
-        <v>2778</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1386</v>
+        <v>692</v>
       </c>
       <c r="C6" t="n">
-        <v>4064</v>
+        <v>2932</v>
       </c>
       <c r="D6" t="n">
-        <v>1176</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>738</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>2487</v>
+        <v>1279</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1199</v>
+        <v>543</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10135</v>
+        <v>1076</v>
       </c>
       <c r="C2" t="n">
-        <v>6830</v>
+        <v>1866</v>
       </c>
       <c r="D2" t="n">
-        <v>33036</v>
+        <v>12082</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4883</v>
+        <v>1599</v>
       </c>
       <c r="C3" t="n">
-        <v>5094</v>
+        <v>3383</v>
       </c>
       <c r="D3" t="n">
-        <v>16433</v>
+        <v>12939</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2756</v>
+        <v>2063</v>
       </c>
       <c r="C4" t="n">
-        <v>5619</v>
+        <v>4889</v>
       </c>
       <c r="D4" t="n">
-        <v>8451</v>
+        <v>7289</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2100</v>
+        <v>1415</v>
       </c>
       <c r="C5" t="n">
-        <v>5196</v>
+        <v>5996</v>
       </c>
       <c r="D5" t="n">
-        <v>3393</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1522</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
-        <v>4436</v>
+        <v>3807</v>
       </c>
       <c r="D6" t="n">
-        <v>1364</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>892</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>3095</v>
+        <v>1262</v>
       </c>
       <c r="D7" t="n">
-        <v>729</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>417</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1703</v>
+        <v>508</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>741</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9199</v>
+        <v>1538</v>
       </c>
       <c r="C2" t="n">
-        <v>4644</v>
+        <v>6981</v>
       </c>
       <c r="D2" t="n">
-        <v>27217</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5426</v>
+        <v>1153</v>
       </c>
       <c r="C3" t="n">
-        <v>8029</v>
+        <v>2247</v>
       </c>
       <c r="D3" t="n">
-        <v>17583</v>
+        <v>11897</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1940</v>
+        <v>1650</v>
       </c>
       <c r="C4" t="n">
-        <v>8062</v>
+        <v>4010</v>
       </c>
       <c r="D4" t="n">
-        <v>7862</v>
+        <v>8097</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1406</v>
+        <v>1544</v>
       </c>
       <c r="C5" t="n">
-        <v>4347</v>
+        <v>5412</v>
       </c>
       <c r="D5" t="n">
-        <v>2248</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="C6" t="n">
-        <v>3033</v>
+        <v>4855</v>
       </c>
       <c r="D6" t="n">
-        <v>714</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>1668</v>
+        <v>2458</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>726</v>
+        <v>840</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5517</v>
+        <v>942</v>
       </c>
       <c r="C2" t="n">
-        <v>2370</v>
+        <v>3994</v>
       </c>
       <c r="D2" t="n">
-        <v>18935</v>
+        <v>9122</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5994</v>
+        <v>1135</v>
       </c>
       <c r="C3" t="n">
-        <v>5902</v>
+        <v>4038</v>
       </c>
       <c r="D3" t="n">
-        <v>17880</v>
+        <v>11330</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2811</v>
+        <v>1361</v>
       </c>
       <c r="C4" t="n">
-        <v>8111</v>
+        <v>3195</v>
       </c>
       <c r="D4" t="n">
-        <v>9267</v>
+        <v>8512</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="C5" t="n">
-        <v>5998</v>
+        <v>4901</v>
       </c>
       <c r="D5" t="n">
-        <v>2923</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="C6" t="n">
-        <v>3642</v>
+        <v>5261</v>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>2189</v>
+        <v>3401</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>990</v>
+        <v>1262</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4878</v>
+        <v>1470</v>
       </c>
       <c r="C2" t="n">
-        <v>3961</v>
+        <v>7792</v>
       </c>
       <c r="D2" t="n">
-        <v>17632</v>
+        <v>11972</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4859</v>
+        <v>882</v>
       </c>
       <c r="C3" t="n">
-        <v>3762</v>
+        <v>3554</v>
       </c>
       <c r="D3" t="n">
-        <v>16973</v>
+        <v>10232</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3605</v>
+        <v>1111</v>
       </c>
       <c r="C4" t="n">
-        <v>6860</v>
+        <v>3549</v>
       </c>
       <c r="D4" t="n">
-        <v>10390</v>
+        <v>8740</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>1373</v>
       </c>
       <c r="C5" t="n">
-        <v>6867</v>
+        <v>3980</v>
       </c>
       <c r="D5" t="n">
-        <v>3808</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>1132</v>
       </c>
       <c r="C6" t="n">
-        <v>4705</v>
+        <v>5094</v>
       </c>
       <c r="D6" t="n">
-        <v>1156</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>532</v>
+        <v>462</v>
       </c>
       <c r="C7" t="n">
-        <v>2836</v>
+        <v>4253</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1481</v>
+        <v>2154</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>603</v>
+        <v>773</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2915</v>
+        <v>964</v>
       </c>
       <c r="C2" t="n">
-        <v>1864</v>
+        <v>3927</v>
       </c>
       <c r="D2" t="n">
-        <v>12329</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4691</v>
+        <v>1256</v>
       </c>
       <c r="C3" t="n">
-        <v>3714</v>
+        <v>5070</v>
       </c>
       <c r="D3" t="n">
-        <v>16661</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3992</v>
+        <v>1807</v>
       </c>
       <c r="C4" t="n">
-        <v>6364</v>
+        <v>5010</v>
       </c>
       <c r="D4" t="n">
-        <v>11178</v>
+        <v>9120</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1940</v>
+        <v>1160</v>
       </c>
       <c r="C5" t="n">
-        <v>7876</v>
+        <v>6509</v>
       </c>
       <c r="D5" t="n">
-        <v>4042</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>944</v>
+        <v>426</v>
       </c>
       <c r="C6" t="n">
-        <v>5665</v>
+        <v>5515</v>
       </c>
       <c r="D6" t="n">
-        <v>1144</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>2891</v>
+        <v>2110</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1040</v>
+        <v>757</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3820</v>
+        <v>489</v>
       </c>
       <c r="C2" t="n">
-        <v>7481</v>
+        <v>2168</v>
       </c>
       <c r="D2" t="n">
-        <v>12853</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3394</v>
+        <v>959</v>
       </c>
       <c r="C3" t="n">
-        <v>2543</v>
+        <v>3939</v>
       </c>
       <c r="D3" t="n">
-        <v>14952</v>
+        <v>9846</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3735</v>
+        <v>1280</v>
       </c>
       <c r="C4" t="n">
-        <v>5020</v>
+        <v>4791</v>
       </c>
       <c r="D4" t="n">
-        <v>11733</v>
+        <v>8897</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2443</v>
+        <v>1044</v>
       </c>
       <c r="C5" t="n">
-        <v>7105</v>
+        <v>5132</v>
       </c>
       <c r="D5" t="n">
-        <v>5054</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1210</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>6602</v>
+        <v>4922</v>
       </c>
       <c r="D6" t="n">
-        <v>1518</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>4061</v>
+        <v>2663</v>
       </c>
       <c r="D7" t="n">
-        <v>635</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1731</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2865</v>
+        <v>797</v>
       </c>
       <c r="C2" t="n">
-        <v>3665</v>
+        <v>7400</v>
       </c>
       <c r="D2" t="n">
-        <v>10025</v>
+        <v>9097</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3093</v>
+        <v>612</v>
       </c>
       <c r="C3" t="n">
-        <v>4084</v>
+        <v>2570</v>
       </c>
       <c r="D3" t="n">
-        <v>13886</v>
+        <v>8571</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3317</v>
+        <v>978</v>
       </c>
       <c r="C4" t="n">
-        <v>4037</v>
+        <v>4200</v>
       </c>
       <c r="D4" t="n">
-        <v>11921</v>
+        <v>8808</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2695</v>
+        <v>1052</v>
       </c>
       <c r="C5" t="n">
-        <v>6469</v>
+        <v>4884</v>
       </c>
       <c r="D5" t="n">
-        <v>5766</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1426</v>
+        <v>656</v>
       </c>
       <c r="C6" t="n">
-        <v>7035</v>
+        <v>4976</v>
       </c>
       <c r="D6" t="n">
-        <v>1835</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
-        <v>4960</v>
+        <v>3861</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>2268</v>
+        <v>1746</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>552</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4644</v>
+        <v>1028</v>
       </c>
       <c r="C2" t="n">
-        <v>3856</v>
+        <v>9976</v>
       </c>
       <c r="D2" t="n">
-        <v>21665</v>
+        <v>18611</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2534</v>
+        <v>574</v>
       </c>
       <c r="C3" t="n">
-        <v>3475</v>
+        <v>4425</v>
       </c>
       <c r="D3" t="n">
-        <v>12533</v>
+        <v>8047</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>706</v>
       </c>
       <c r="C4" t="n">
-        <v>3973</v>
+        <v>3211</v>
       </c>
       <c r="D4" t="n">
-        <v>11841</v>
+        <v>8497</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2679</v>
+        <v>930</v>
       </c>
       <c r="C5" t="n">
-        <v>5330</v>
+        <v>4427</v>
       </c>
       <c r="D5" t="n">
-        <v>6417</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1707</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>6751</v>
+        <v>4876</v>
       </c>
       <c r="D6" t="n">
-        <v>2284</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>611</v>
+        <v>368</v>
       </c>
       <c r="C7" t="n">
-        <v>5799</v>
+        <v>4405</v>
       </c>
       <c r="D7" t="n">
-        <v>851</v>
+        <v>969</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>3216</v>
+        <v>2740</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>1178</v>
+        <v>1090</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6408</v>
+        <v>8292</v>
       </c>
       <c r="C2" t="n">
-        <v>4156</v>
+        <v>11240</v>
       </c>
       <c r="D2" t="n">
-        <v>4949</v>
+        <v>9569</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3323</v>
+        <v>1056</v>
       </c>
       <c r="C2" t="n">
-        <v>2190</v>
+        <v>14587</v>
       </c>
       <c r="D2" t="n">
-        <v>15945</v>
+        <v>21673</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3454</v>
+        <v>629</v>
       </c>
       <c r="C3" t="n">
-        <v>3863</v>
+        <v>6114</v>
       </c>
       <c r="D3" t="n">
-        <v>14213</v>
+        <v>8942</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3911</v>
+        <v>566</v>
       </c>
       <c r="C4" t="n">
-        <v>5818</v>
+        <v>3696</v>
       </c>
       <c r="D4" t="n">
-        <v>12111</v>
+        <v>8165</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1651</v>
+        <v>764</v>
       </c>
       <c r="C5" t="n">
-        <v>8772</v>
+        <v>3762</v>
       </c>
       <c r="D5" t="n">
-        <v>5739</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>564</v>
+        <v>780</v>
       </c>
       <c r="C6" t="n">
-        <v>7006</v>
+        <v>4625</v>
       </c>
       <c r="D6" t="n">
-        <v>1844</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>3151</v>
+        <v>4567</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>1154</v>
+        <v>3456</v>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>1768</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>642</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7294</v>
+        <v>7766</v>
       </c>
       <c r="C2" t="n">
-        <v>5492</v>
+        <v>6872</v>
       </c>
       <c r="D2" t="n">
-        <v>10896</v>
+        <v>11696</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2722</v>
+        <v>2735</v>
       </c>
       <c r="C3" t="n">
-        <v>2127</v>
+        <v>4438</v>
       </c>
       <c r="D3" t="n">
-        <v>1510</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6289</v>
+        <v>4048</v>
       </c>
       <c r="C2" t="n">
-        <v>8628</v>
+        <v>3089</v>
       </c>
       <c r="D2" t="n">
-        <v>12816</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4112</v>
+        <v>4426</v>
       </c>
       <c r="C3" t="n">
+        <v>5064</v>
+      </c>
+      <c r="D3" t="n">
         <v>3499</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2975</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1216</v>
+        <v>1287</v>
       </c>
       <c r="C4" t="n">
-        <v>1309</v>
+        <v>2816</v>
       </c>
       <c r="D4" t="n">
-        <v>1485</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5537</v>
+        <v>3621</v>
       </c>
       <c r="C2" t="n">
-        <v>10775</v>
+        <v>5459</v>
       </c>
       <c r="D2" t="n">
-        <v>17916</v>
+        <v>16260</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4302</v>
+        <v>3494</v>
       </c>
       <c r="C3" t="n">
-        <v>5449</v>
+        <v>3379</v>
       </c>
       <c r="D3" t="n">
-        <v>4335</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2255</v>
+        <v>2509</v>
       </c>
       <c r="C4" t="n">
-        <v>2509</v>
+        <v>4095</v>
       </c>
       <c r="D4" t="n">
-        <v>1725</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>559</v>
+        <v>596</v>
       </c>
       <c r="C5" t="n">
-        <v>821</v>
+        <v>1705</v>
       </c>
       <c r="D5" t="n">
-        <v>1193</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6054</v>
+        <v>2654</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>5759</v>
       </c>
       <c r="D2" t="n">
-        <v>24739</v>
+        <v>30361</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4024</v>
+        <v>2966</v>
       </c>
       <c r="C3" t="n">
-        <v>7162</v>
+        <v>3906</v>
       </c>
       <c r="D3" t="n">
-        <v>6094</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2760</v>
+        <v>2570</v>
       </c>
       <c r="C4" t="n">
-        <v>4065</v>
+        <v>3604</v>
       </c>
       <c r="D4" t="n">
-        <v>2132</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1173</v>
+        <v>1323</v>
       </c>
       <c r="C5" t="n">
-        <v>1695</v>
+        <v>2960</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>560</v>
+        <v>1034</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6151</v>
+        <v>2350</v>
       </c>
       <c r="C2" t="n">
-        <v>10103</v>
+        <v>7499</v>
       </c>
       <c r="D2" t="n">
-        <v>35412</v>
+        <v>31996</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3663</v>
+        <v>2337</v>
       </c>
       <c r="C3" t="n">
-        <v>5099</v>
+        <v>4229</v>
       </c>
       <c r="D3" t="n">
-        <v>7995</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2120</v>
+        <v>2392</v>
       </c>
       <c r="C4" t="n">
-        <v>4698</v>
+        <v>3691</v>
       </c>
       <c r="D4" t="n">
-        <v>2416</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1021</v>
+        <v>1669</v>
       </c>
       <c r="C5" t="n">
-        <v>2158</v>
+        <v>3203</v>
       </c>
       <c r="D5" t="n">
-        <v>1115</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>352</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>759</v>
+        <v>2002</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>292</v>
+        <v>664</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5555</v>
+        <v>2281</v>
       </c>
       <c r="C2" t="n">
-        <v>5640</v>
+        <v>5678</v>
       </c>
       <c r="D2" t="n">
-        <v>29208</v>
+        <v>26010</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4074</v>
+        <v>1942</v>
       </c>
       <c r="C3" t="n">
-        <v>6934</v>
+        <v>5087</v>
       </c>
       <c r="D3" t="n">
-        <v>12219</v>
+        <v>11914</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2539</v>
+        <v>2058</v>
       </c>
       <c r="C4" t="n">
-        <v>4846</v>
+        <v>3887</v>
       </c>
       <c r="D4" t="n">
-        <v>3520</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1392</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>3624</v>
+        <v>3375</v>
       </c>
       <c r="D5" t="n">
-        <v>1343</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>640</v>
+        <v>1029</v>
       </c>
       <c r="C6" t="n">
-        <v>1555</v>
+        <v>2526</v>
       </c>
       <c r="D6" t="n">
-        <v>809</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>557</v>
+        <v>1293</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>261</v>
+        <v>465</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5080</v>
+        <v>2139</v>
       </c>
       <c r="C2" t="n">
-        <v>9087</v>
+        <v>3497</v>
       </c>
       <c r="D2" t="n">
-        <v>27574</v>
+        <v>20412</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3947</v>
+        <v>3093</v>
       </c>
       <c r="C3" t="n">
-        <v>5391</v>
+        <v>7234</v>
       </c>
       <c r="D3" t="n">
-        <v>14057</v>
+        <v>12922</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2825</v>
+        <v>1630</v>
       </c>
       <c r="C4" t="n">
-        <v>5927</v>
+        <v>5665</v>
       </c>
       <c r="D4" t="n">
-        <v>5083</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1732</v>
+        <v>950</v>
       </c>
       <c r="C5" t="n">
-        <v>4182</v>
+        <v>2475</v>
       </c>
       <c r="D5" t="n">
-        <v>1686</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>916</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>2649</v>
+        <v>1267</v>
       </c>
       <c r="D6" t="n">
-        <v>895</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>1084</v>
+        <v>455</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>411</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
